--- a/수강생_정밀분석_최종본.xlsx
+++ b/수강생_정밀분석_최종본.xlsx
@@ -7673,7 +7673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C428"/>
+  <dimension ref="A1:C441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7696,29 +7696,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Emal풍우고</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99893569880195988958098712579898911988777498706879985112</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>033-1261-9937</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Emal풍우고</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024343502434263230118230213</t>
+          <t>010-5165-5152</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7730,12 +7726,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>강지연</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>803-462-0632</t>
+          <t>010-3411-3469</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -7743,12 +7739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강지연</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>060-8744-2766</t>
+          <t>795-010-2529</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7760,12 +7756,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강지연</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>010-9296-4452</t>
+          <t>010-4423-7821</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7777,12 +7773,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고한별</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>529-010-3940</t>
+          <t>010-2713-7720</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7794,72 +7790,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>고한별</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>470107373</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>904-362-3919</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>권성운</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>870-2481-0843</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>810-5267-5076</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>권성운</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>916-550-8210</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>010-8975-5327</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>권성운</t>
+          <t>(이름 확인필요)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>010-4909-3277</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2014-6211</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>권수빈</t>
+          <t>강지연</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>005-195-4115</t>
+          <t>060-8744-2766</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7871,25 +7867,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>권수빈</t>
+          <t>강지연</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>010-3285-5451</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>010-9296-4452</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>기민지</t>
+          <t>강지연</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>010-7779-0677</t>
+          <t>803-462-0632</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -7897,85 +7897,89 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>기민지</t>
+          <t>고한별</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>010-5656-1650</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>470107373</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>기아영</t>
+          <t>고한별</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>010-4716-4612</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>529-010-3940</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>기아영</t>
+          <t>권성운</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>904-706-4612</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>870-2481-0843</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>김관웅</t>
+          <t>권성운</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>010-5293-3318</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>010-4909-3277</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권성운</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>010-2933-2837</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>916-550-8210</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권수빈</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>003-381-0099</t>
+          <t>005-195-4115</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7987,46 +7991,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권수빈</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>010-8842-9444</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3285-5451</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>기민지</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>010-4323-1315</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5656-1650</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>기민지</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>010-8083-2315</t>
+          <t>010-7779-0677</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -8034,42 +8030,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>기아영</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>010-9939-9315</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>904-706-4612</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김관웅</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>010-8855-9990</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5293-3318</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김기현</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>010-2247-2195</t>
+          <t>010-8865-0471</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8081,38 +8077,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>010-5368-2690</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>010-4323-1315</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>010-010-0100</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>010-2933-2837</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>010-4260-5320</t>
+          <t>003-381-0099</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8124,12 +8128,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>010-4752-6297</t>
+          <t>010-8842-9444</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8141,12 +8145,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김다은</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>918-7479-8818</t>
+          <t>010-9939-9315</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -8154,29 +8158,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김다은</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>010-2058-3571</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8083-2315</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김다창</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>010-6392-9086</t>
+          <t>010-5368-2690</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -8184,12 +8184,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>김도현</t>
+          <t>김다창</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>010-858-5346</t>
+          <t>010-2247-2195</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8201,12 +8201,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>김도현</t>
+          <t>김다창</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>010-2649-0101</t>
+          <t>010-8855-9990</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8218,115 +8218,119 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>김명준</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>010-6342-1892</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>010-2058-3571</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>김명준</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>010-2361-7882</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>010-4752-6297</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>010010010</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>010-4260-5320</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>418-010-9648</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6392-9086</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>010-2897-1638</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>918-7479-8818</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>010-4803-0310</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-010-0100</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도현</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>010-8608-6520</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>010-2649-0101</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>김도현</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>010-3436-1638</t>
+          <t>010-858-5346</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8338,12 +8342,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>김민수</t>
+          <t>김명준</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>003-181-2003</t>
+          <t>010-6342-1892</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -8351,12 +8355,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>김서은</t>
+          <t>김명준</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>167937577</t>
+          <t>010-2361-7882</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -8364,12 +8368,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>김서은</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>010-229-9757</t>
+          <t>418-010-9648</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8381,38 +8385,46 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>김서은</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>010-7670-2891</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>010-2897-1638</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>김선유</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>010-3477-4410</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>010-4803-0310</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>김선유</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>010-9522-4410</t>
+          <t>010-3436-1638</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8424,63 +8436,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>김선희</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>181-010-5611</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8608-6520</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>김선희</t>
+          <t>김미</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>202-010-2644</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010010010</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>김선희</t>
+          <t>김민수</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>010-5264-0738</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>003-181-2003</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>김성은</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>010-9866-1616</t>
+          <t>010-5162-0228</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8492,25 +8492,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>김성은</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>010-3065-3322</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>010-2196-6510</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>643-010-9518</t>
+          <t>010-9871-9855</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8522,12 +8526,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>010-2643-3860</t>
+          <t>010-625-1230</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8539,25 +8543,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02-063-1849</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>010-2845-3845</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>010-2337-2197</t>
+          <t>010-3123-0038</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8569,46 +8577,38 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>김서은</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>280102590</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7670-2891</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>김소연</t>
+          <t>김서은</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>438531116</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>167937577</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>김소연</t>
+          <t>김서은</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>010-3192-4180</t>
+          <t>010-229-9757</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8620,68 +8620,76 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>김소연</t>
+          <t>김선유</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>010-9411-5494</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3477-4410</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>김소중</t>
+          <t>김선유</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>010-8702-9829</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>010-9522-4410</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>김소중</t>
+          <t>김선희</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>010-2948-0380</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>181-010-5611</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>김송익</t>
+          <t>김선희</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>010-9047-5710</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>010-5264-0738</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>김송익</t>
+          <t>김선희</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>010-5002-5710</t>
+          <t>202-010-2644</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8693,12 +8701,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>김성은</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>010-5587-3910</t>
+          <t>010-9866-1616</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8710,46 +8718,38 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>김예빈</t>
+          <t>김성은</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>010-8372-3369</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3065-3322</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>김예빈</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>010-4451-9576</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>02-063-1849</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>김용민</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>463-010-3420</t>
+          <t>010-2643-3860</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8761,12 +8761,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>김용민</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0010302382900</t>
+          <t>643-010-9518</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8778,12 +8778,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>김유정</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>010-2323-4517</t>
+          <t>280102590</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8795,12 +8795,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>김유정</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>010-9297-4166</t>
+          <t>010-2337-2197</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8812,12 +8812,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>김유정</t>
+          <t>김소연</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>002-443-0554</t>
+          <t>010-9411-5494</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8829,12 +8829,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>김재민</t>
+          <t>김소연</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>010-228-4722</t>
+          <t>438531116</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8846,12 +8846,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>김재민</t>
+          <t>김소연</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>010-4908-3421</t>
+          <t>010-3192-4180</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8863,63 +8863,51 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>김재민</t>
+          <t>김소중</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>010-3340-3421</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8702-9829</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>김재훈일시</t>
+          <t>김소중</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>010-7705-3658</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2948-0380</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>김재훈일시</t>
+          <t>김송익</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>010-3424-8456</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-9047-5710</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>김재훈일시</t>
+          <t>김송익</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>010-5851-2600</t>
+          <t>010-5002-5710</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8931,12 +8919,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>김주승</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>010-4057-7636</t>
+          <t>010-5587-3910</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8948,12 +8936,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>김주승</t>
+          <t>김예빈</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>010-8595-4112</t>
+          <t>010-8372-3369</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8965,12 +8953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>김주승</t>
+          <t>김예빈</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>210-4083-4285</t>
+          <t>010-4451-9576</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8982,12 +8970,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>김하유</t>
+          <t>김용민</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>010-2196-6510</t>
+          <t>463-010-3420</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8999,12 +8987,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>김하유</t>
+          <t>김용민</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>010-9871-9855</t>
+          <t>0010302382900</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9016,12 +9004,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>김하유</t>
+          <t>김유정</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>010-3123-0038</t>
+          <t>002-443-0554</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9033,12 +9021,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>김하유</t>
+          <t>김유정</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>010-9260-9106</t>
+          <t>010-9297-4166</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9050,12 +9038,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>김하은</t>
+          <t>김유정</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>000-5911-4666</t>
+          <t>010-2323-4517</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9067,12 +9055,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>김효나</t>
+          <t>김재민</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>010-8470-7179</t>
+          <t>010-228-4722</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9084,51 +9072,63 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>김효나</t>
+          <t>김재민</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>010-8213-0961</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>010-4908-3421</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>김희정</t>
+          <t>김재민</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>010-5838-0624</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>010-3340-3421</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>김희정</t>
+          <t>김재훈일시</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>010-3146-0116</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>010-5851-2600</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>깅은희</t>
+          <t>김재훈일시</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>010-6725-5155</t>
+          <t>010-7705-3658</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9140,25 +9140,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>깅은희</t>
+          <t>김재훈일시</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>010-7688-5132</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>010-3424-8456</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>김주승</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>010-4118-0184</t>
+          <t>210-4083-4285</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9170,12 +9174,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>김주승</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>010-5915-4450</t>
+          <t>010-8595-4112</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9187,12 +9191,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>김주승</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>010-3923-4450</t>
+          <t>010-4057-7636</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9204,12 +9208,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>김지민</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>010-7321-5702</t>
+          <t>010-9260-9106</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9221,42 +9225,42 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>김지우</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>010-5120-8254</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8618-3417</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>031-606-3003</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>010-4715-6937</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>052-714-8429</t>
+          <t>000-5911-4666</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9268,12 +9272,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>김효나</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>02-547-5233</t>
+          <t>010-8213-0961</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -9281,12 +9285,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>김효나</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>02-0542-01720</t>
+          <t>010-8470-7179</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9298,59 +9302,55 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>김희정</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>010-5212-6755</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5838-0624</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>김희정</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>693-010-2346</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3146-0116</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>락본인</t>
+          <t>깅은희</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>010-8618-3417</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>010-6725-5155</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>문다빈</t>
+          <t>깅은희</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>010-4616-2481</t>
+          <t>010-7688-5132</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -9358,25 +9358,29 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>문다빈</t>
+          <t>남이정</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>010-4374-5352</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>010-5120-8254</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>문준석</t>
+          <t>남이정</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>010-8874-7107</t>
+          <t>010-3923-4450</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9388,25 +9392,29 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>남이정</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>010-9217-0042</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>010-5915-4450</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>남이정</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>010-8132-8306</t>
+          <t>010-7321-5702</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9418,25 +9426,29 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>남이정</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>208-532-2306</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>010-4118-0184</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>동광역집쌀유</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>010-8217-0042</t>
+          <t>02-547-5233</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -9444,81 +9456,93 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>동광역집쌀유</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>010-7243-6763</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>052-714-8429</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>동광역집쌀유</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>010-3343-8064</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>031-606-3003</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>031-298-6763</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>693-010-2346</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>민원기</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>010-5778-3650</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>02-0542-01720</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>민준흥</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>010-8882-3026</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>008-654-7364</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>박서준</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>004-937-8477</t>
+          <t>512082545</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9530,25 +9554,29 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>박서준</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>010-4525-8476</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>218073646</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>박서후</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>182-010-9269</t>
+          <t>010-5212-6755</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9560,106 +9588,98 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>박성현</t>
+          <t>문다빈</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>010-3496-4008</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4616-2481</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>박성화</t>
+          <t>문다빈</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>010-4671-8633</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4374-5352</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>박성화</t>
+          <t>문준석</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>636-484-2665</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>010-8874-7107</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>박성화</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>010-5320-8634</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8217-0042</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>박어경</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>058200026</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-9217-0042</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>박어경</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>010-7619-0025</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>010-8132-8306</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>박은력</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>810-4405-6360</t>
+          <t>208-532-2306</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -9667,46 +9687,38 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>박은력</t>
+          <t>민숙경</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>010-3772-6360</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>031-298-6763</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>박이소</t>
+          <t>민숙경</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>010-6328-2348</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7243-6763</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>박이소</t>
+          <t>민숙경</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>010-3688-5475</t>
+          <t>010-3343-8064</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9718,12 +9730,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>박재웅</t>
+          <t>민원기</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>010-2088-4787</t>
+          <t>010-5778-3650</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -9731,42 +9743,42 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>박재웅</t>
+          <t>민준흥</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>010-3286-3005</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8882-3026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>박정진</t>
+          <t>박서준</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>010-8458-1321</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>004-937-8477</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>박정진</t>
+          <t>박서준</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>008-748-7321</t>
+          <t>010-4525-8476</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -9774,38 +9786,46 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>박지승</t>
+          <t>박서후</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>004-150-0852</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>182-010-9269</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>박하는</t>
+          <t>박성현</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>010-3042-6365</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>010-3496-4008</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>박하는</t>
+          <t>박성화</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>004135124</t>
+          <t>010-5320-8634</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9817,12 +9837,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>박하람</t>
+          <t>박성화</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>010-392-6094</t>
+          <t>010-4671-8633</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9834,29 +9854,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>박하람</t>
+          <t>박성화</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>010-8236-6094</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>636-484-2665</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>박하랑</t>
+          <t>박어경</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>010-6763-3954</t>
+          <t>010-7619-0025</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -9864,12 +9880,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>박행님</t>
+          <t>박어경</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>010-3619-0021</t>
+          <t>058200026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9881,29 +9897,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>박행님</t>
+          <t>박은력</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>010-1290-4454</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-4405-6360</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>박은력</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0189691682433042</t>
+          <t>010-3772-6360</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9915,12 +9927,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>박이소</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>158-010-4355</t>
+          <t>010-6328-2348</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9932,12 +9944,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>박이소</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>010-5296-7701</t>
+          <t>010-3688-5475</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9949,12 +9961,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>박재웅</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>00010010000000</t>
+          <t>010-2088-4787</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -9962,12 +9974,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>박재웅</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>010-3123-8001</t>
+          <t>010-3286-3005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9979,106 +9991,98 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>박정진</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>010-8223-3092</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8458-1321</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>박정진</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>010-2042-6369</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>008-748-7321</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>박지승</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>383-010-9249</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-150-0852</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>박하는</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>010-3092-5988</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3042-6365</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>박하는</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01001001001001000</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>004135124</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>박하람</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>459-845-5310</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>010-8236-6094</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>박하람</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>010-9461-4643</t>
+          <t>010-392-6094</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10090,29 +10094,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>박하랑</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>010-2633-3685</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6763-3954</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>박행님</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>945782420115</t>
+          <t>010-1290-4454</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10124,94 +10124,110 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>서아론</t>
+          <t>박행님</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>010-5646-5801</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>010-3619-0021</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>서아론</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>005-346-4576</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>158-010-4355</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>세종요리제과기술학원</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>031-986-1933</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>010-3123-8001</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>010259338</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>00010010000000</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>904-480-3821</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>010-5296-7701</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>010-2751-8260</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
+          <t>0189691682433042</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>배해란</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>801094618260</t>
+          <t>010-2042-6369</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10223,25 +10239,29 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>손진형</t>
+          <t>배해란</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>110-3896-1169</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>383-010-9249</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>배해란</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>210-8375-3274</t>
+          <t>010-3092-5988</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10253,12 +10273,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>배해란</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>010-3887-3274</t>
+          <t>010-8223-3092</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10270,25 +10290,29 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01000010010010010</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>010-2633-3685</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>87549457</t>
+          <t>010-9461-4643</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10300,76 +10324,68 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>송하린</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>010-8729-5933</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>945782420115</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>승손에요</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>010-2540-5528</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>459-845-5310</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>승손에요</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>010-0428-7130</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01001001001001000</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>승손에요</t>
+          <t>서아론</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>010-9138-7130</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>005-346-4576</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>서아론</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>010-7202-7169</t>
+          <t>010-5646-5801</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -10377,12 +10393,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>세종요리제과기술학원</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>010-2447-2733</t>
+          <t>031-986-1933</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -10390,25 +10406,29 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>004-187-2733</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>010259338</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>010-6390-7152</t>
+          <t>904-480-3821</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -10416,12 +10436,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>신지응</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>108-325-9659</t>
+          <t>010-2751-8260</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -10429,42 +10449,42 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>신지응</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>010-5136-9658</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>801094618260</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>손진형</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>09876670</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>110-3896-1169</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>001-517-6315</t>
+          <t>210-8375-3274</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10476,29 +10496,25 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>010-5240-3831</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01000010010010010</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>835-010-2364</t>
+          <t>87549457</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10510,12 +10526,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>010-4740-6511</t>
+          <t>010-3887-3274</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10527,29 +10543,25 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>송하린</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>504-010-5241</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8729-5933</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>승손에요</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>010-2100-6423</t>
+          <t>010-2540-5528</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10561,12 +10573,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>아비지</t>
+          <t>승손에요</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>10109653</t>
+          <t>010-9138-7130</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10578,12 +10590,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>안건하다</t>
+          <t>승손에요</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>005689040</t>
+          <t>010-0428-7130</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10595,63 +10607,51 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>안건하다</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>010176443878</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2447-2733</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>안세은</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>006-818-3587</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6390-7152</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>636121922</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7202-7169</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>010-0321-2799</t>
+          <t>004-187-2733</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -10659,59 +10659,55 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>신지응</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>010-239-2903</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>108-325-9659</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>양재준</t>
+          <t>신지응</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>901603211</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5136-9658</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>양재준</t>
+          <t>신학림</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>003-008-1295</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>010-5240-3831</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>양정인</t>
+          <t>신학림</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>010-8443-1396</t>
+          <t>001-517-6315</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10723,12 +10719,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>양정인</t>
+          <t>신학림</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>010-3798-3144</t>
+          <t>09876670</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10740,25 +10736,29 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>여민욱</t>
+          <t>신혁진</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>010-3319-0845</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
+          <t>835-010-2364</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>여민욱</t>
+          <t>신혁진</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>010-3337-6745</t>
+          <t>504-010-5241</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10770,12 +10770,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>여승원</t>
+          <t>신혁진</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>010527747270026111360</t>
+          <t>010-2100-6423</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -10787,12 +10787,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>여승원</t>
+          <t>신혁진</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>008-532-1360</t>
+          <t>010-4740-6511</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -10804,12 +10804,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>염지웅</t>
+          <t>아비지</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>010-6351-1537</t>
+          <t>10109653</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -10821,38 +10821,46 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>염지웅</t>
+          <t>안건하다</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>810-3982-4645</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>010176443878</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>오먼걸</t>
+          <t>안건하다</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>004-036-2289</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
+          <t>005689040</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>오지원</t>
+          <t>안세은</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>010-9379-3486</t>
+          <t>006-818-3587</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -10864,29 +10872,25 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>오지원</t>
+          <t>안시우</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>610-8580-3486</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-0321-2799</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>왕다영</t>
+          <t>안시우</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>010-4362-3019</t>
+          <t>636121922</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -10898,12 +10902,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>왕다영</t>
+          <t>안시우</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>010-8365-0471</t>
+          <t>010-239-2903</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -10915,29 +10919,25 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>왕다영</t>
+          <t>양재준</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>900-7312-7844</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>003-008-1295</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>왕성지</t>
+          <t>양재준</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>910990847</t>
+          <t>901603211</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10949,25 +10949,29 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>왕옹유</t>
+          <t>양정인</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>010-3140-8826</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>010-8443-1396</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>왕옹유</t>
+          <t>양정인</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>120102529</t>
+          <t>010-3798-3144</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -10979,12 +10983,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>운승혁</t>
+          <t>여민욱</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>010-2066-2281</t>
+          <t>010-3319-0845</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -10992,12 +10996,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>운승혁</t>
+          <t>여민욱</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>004491365</t>
+          <t>010-3337-6745</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11009,25 +11013,29 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>위묘한</t>
+          <t>여승원</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>010-8627-8972</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
+          <t>010527747270026111360</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>위묘한</t>
+          <t>여승원</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>010-8750-8992</t>
+          <t>008-532-1360</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11039,12 +11047,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>위요한</t>
+          <t>염지웅</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>010-3763-3610</t>
+          <t>010-6351-1537</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11056,46 +11064,38 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>위요한</t>
+          <t>염지웅</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>010-8627-8972</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-3982-4645</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>위요한</t>
+          <t>오먼걸</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>010-8750-8992</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-036-2289</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>유나오가스유나영강</t>
+          <t>오지원</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>643-010-3750</t>
+          <t>610-8580-3486</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -11107,12 +11107,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>유나오가스유나영강</t>
+          <t>오지원</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>010-5207-6881</t>
+          <t>010-9379-3486</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -11124,12 +11124,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>유나오가스유나영강</t>
+          <t>왕다영</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>010-2367-4628</t>
+          <t>010-8365-0471</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -11141,12 +11141,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>유나오가스유나영강</t>
+          <t>왕다영</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>010-9600-0012</t>
+          <t>900-7312-7844</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -11158,12 +11158,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>유리</t>
+          <t>왕다영</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>010-5458-5770</t>
+          <t>010-4362-3019</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -11175,12 +11175,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>유리</t>
+          <t>왕성지</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>010-5611-0822</t>
+          <t>910990847</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -11192,12 +11192,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>유민지</t>
+          <t>왕옹유</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>010-6263-0556</t>
+          <t>010-3140-8826</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -11205,25 +11205,29 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>유민지</t>
+          <t>왕옹유</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>010-8988-0556</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
+          <t>120102529</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>유민지</t>
+          <t>운승혁</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>010-0108-0556</t>
+          <t>010-2066-2281</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -11231,68 +11235,76 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>유용우</t>
+          <t>운승혁</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>200-2752-8294</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
+          <t>004491365</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>유원민</t>
+          <t>위묘한</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>773-866-8766</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8627-8972</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>유원민</t>
+          <t>위묘한</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>010010010</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
+          <t>010-8750-8992</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>유원민</t>
+          <t>위요한</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>17266727</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
+          <t>010-8627-8972</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>유원민</t>
+          <t>위요한</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>807-010-8322</t>
+          <t>010-8750-8992</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11304,12 +11316,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>유원민</t>
+          <t>위요한</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>605-010-3821</t>
+          <t>010-3763-3610</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -11321,12 +11333,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>유진성</t>
+          <t>유나오가스유나영강</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>010-5380-0978</t>
+          <t>010-5207-6881</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -11338,12 +11350,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>유진성</t>
+          <t>유나오가스유나영강</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>005-161-8958</t>
+          <t>010-2367-4628</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -11355,25 +11367,29 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>유태한</t>
+          <t>유나오가스유나영강</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>008-489-9717</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>643-010-3750</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>윤수한</t>
+          <t>유나오가스유나영강</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>010-7622-9381</t>
+          <t>010-9600-0012</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -11385,12 +11401,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>윤수한</t>
+          <t>유리</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>010-3186-9381</t>
+          <t>010-5611-0822</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -11402,12 +11418,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>윤종호</t>
+          <t>유리</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>010-8208-9269</t>
+          <t>010-5458-5770</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -11419,29 +11435,25 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>윤종호</t>
+          <t>유민지</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>475789276</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-0108-0556</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>윤종호</t>
+          <t>유민지</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>010-2384-2350</t>
+          <t>010-6263-0556</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -11449,119 +11461,115 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>윤진우</t>
+          <t>유민지</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>684464689</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8988-0556</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>윤진우</t>
+          <t>유용우</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>448434687</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>200-2752-8294</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>윤희라</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>009-980-2112</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
+          <t>773-866-8766</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>의재의</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>120104112</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
+          <t>605-010-3821</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>이경희</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>010-2008-6384</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
+          <t>807-010-8322</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>이금비</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>010-2828-0171</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>17266727</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>이금비</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>010-4663-2519</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010010010</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>이금비</t>
+          <t>유진성</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>208-710-4252</t>
+          <t>005-161-8958</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11573,25 +11581,29 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>이금비</t>
+          <t>유진성</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>010-7337-0882</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
+          <t>010-5380-0978</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>이나경</t>
+          <t>유태한</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>010-7735-0405</t>
+          <t>008-489-9717</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -11599,12 +11611,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>이나경</t>
+          <t>윤수한</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>75908465</t>
+          <t>010-3186-9381</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11616,12 +11628,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>이다운</t>
+          <t>윤수한</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>010-9008-9392</t>
+          <t>010-7622-9381</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11633,12 +11645,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>이다운</t>
+          <t>윤종호</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>010-4475-5834</t>
+          <t>475789276</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11650,29 +11662,25 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>이다운</t>
+          <t>윤종호</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>010-6404-5266</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2384-2350</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>이다운</t>
+          <t>윤종호</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>690106361</t>
+          <t>010-8208-9269</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11684,12 +11692,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>이다정</t>
+          <t>윤진우</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>004-306-3028</t>
+          <t>684464689</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11701,12 +11709,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>이다정</t>
+          <t>윤진우</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>890-0843-6858</t>
+          <t>448434687</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11718,63 +11726,51 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>이다정</t>
+          <t>윤희라</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>010-2767-0893</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>009-980-2112</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>이다정</t>
+          <t>의재의</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>010-8930-1658</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>120104112</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>이동은</t>
+          <t>이경희</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>010-2456-0685</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2008-6384</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>이동은</t>
+          <t>이금비</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>092617358</t>
+          <t>208-710-4252</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11786,29 +11782,25 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>이든지</t>
+          <t>이금비</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>010-2455-8443</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7337-0882</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>이든지</t>
+          <t>이금비</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>010-9600-0012</t>
+          <t>010-2828-0171</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11820,25 +11812,29 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>이든지</t>
+          <t>이금비</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>010-3970-6405</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
+          <t>010-4663-2519</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>이민지대시</t>
+          <t>이나경</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>006-894-1641</t>
+          <t>010-7735-0405</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -11846,12 +11842,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>이민지대시</t>
+          <t>이나경</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>010-9974-3970</t>
+          <t>75908465</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11863,12 +11859,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>이민지대시</t>
+          <t>이다운</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>010-2057-0087</t>
+          <t>010-9008-9392</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11880,12 +11876,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>이방상</t>
+          <t>이다운</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>010-8614-8745</t>
+          <t>690106361</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11897,12 +11893,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>이방상</t>
+          <t>이다운</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>010-9472-9371</t>
+          <t>010-4475-5834</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -11914,12 +11910,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>이방상</t>
+          <t>이다운</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>010-5612-4249</t>
+          <t>010-6404-5266</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -11931,25 +11927,29 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>이상혁</t>
+          <t>이다정</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>010-4706-9331</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+          <t>890-0843-6858</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이다정</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>333-010-2490</t>
+          <t>004-306-3028</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -11961,12 +11961,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이다정</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>092-010-2744</t>
+          <t>010-8930-1658</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -11978,12 +11978,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이다정</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>777315248</t>
+          <t>010-2767-0893</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11995,25 +11995,29 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이동은</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>010010010010010010</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
+          <t>010-2456-0685</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이동은</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>861-010-6226</t>
+          <t>092617358</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12025,42 +12029,42 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>이소미</t>
+          <t>이든지</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>010-963-2501</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3970-6405</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>이소미</t>
+          <t>이든지</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>808-482-6377</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
+          <t>010-2455-8443</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>이송연</t>
+          <t>이든지</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>008649064</t>
+          <t>010-9600-0012</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12072,12 +12076,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>이수경</t>
+          <t>이민지대시</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>010-4046-3924</t>
+          <t>010-2057-0087</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12089,12 +12093,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>이수경</t>
+          <t>이민지대시</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>010-2834-3924</t>
+          <t>010-9974-3970</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12106,55 +12110,59 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>이수아</t>
+          <t>이민지대시</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>010-264-3088</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>006-894-1641</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>이수호</t>
+          <t>이방상</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>010-5448-9196</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
+          <t>010-5612-4249</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>이수호</t>
+          <t>이방상</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>005-450-9186</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr"/>
+          <t>010-9472-9371</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>이승수양</t>
+          <t>이방상</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>010-4344-5525</t>
+          <t>010-8614-8745</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12166,12 +12174,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>이승준</t>
+          <t>이상혁</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>010-8442-8651</t>
+          <t>010-4706-9331</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -12179,42 +12187,42 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>이승준</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>010-3381-8651</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
+          <t>777315248</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>이승환</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>010-8727-6539</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010010010010010010</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>이승환</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>003-562-4517</t>
+          <t>092-010-2744</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12226,12 +12234,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>이승환</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>010-9889-6539</t>
+          <t>333-010-2490</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12243,55 +12251,59 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>이승환</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>004-769-6662</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
+          <t>861-010-6226</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>이예영</t>
+          <t>이소미</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>010-9496-2605</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>808-482-6377</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>이예영</t>
+          <t>이소미</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>010-2832-5092</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
+          <t>010-963-2501</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>이예영</t>
+          <t>이송연</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>010-454-1089</t>
+          <t>008649064</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -12303,12 +12315,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>이우복</t>
+          <t>이수경</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>010-7120-1098</t>
+          <t>010-4046-3924</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12320,12 +12332,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>이우복</t>
+          <t>이수경</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>470102731</t>
+          <t>010-2834-3924</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -12337,12 +12349,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>이우복</t>
+          <t>이수아</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>010-7335-8461</t>
+          <t>010-264-3088</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -12354,46 +12366,38 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>이우복</t>
+          <t>이수호</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>010-2107-1654</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>005-450-9186</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>이웅재</t>
+          <t>이수호</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>02-934-7067</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5448-9196</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>이웅재</t>
+          <t>이승수양</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>9004064150975864</t>
+          <t>010-4344-5525</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -12405,46 +12409,38 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>이웅재</t>
+          <t>이승준</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>010-4555-2991</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3381-8651</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>이유</t>
+          <t>이승준</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>010-8351-4588</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8442-8651</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>이유</t>
+          <t>이승환</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>010-2763-6919</t>
+          <t>010-9889-6539</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12456,12 +12452,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>이유</t>
+          <t>이승환</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>010-9826-4774</t>
+          <t>003-562-4517</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -12473,12 +12469,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>이은서</t>
+          <t>이승환</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>010-4440-8951</t>
+          <t>004-769-6662</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -12486,12 +12482,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>이은정</t>
+          <t>이승환</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>010-2071-5849</t>
+          <t>010-8727-6539</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -12503,12 +12499,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>이은정</t>
+          <t>이아영</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>010-4624-6448</t>
+          <t>010-4716-4612</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -12520,12 +12516,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>이은정</t>
+          <t>이아인</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>010-2467-7493</t>
+          <t>010-9918-5123</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12537,42 +12533,42 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>이은정</t>
+          <t>이예영</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>30153225</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr"/>
+          <t>010-9496-2605</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>이정우</t>
+          <t>이예영</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>120103080</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2832-5092</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>이정우</t>
+          <t>이예영</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>03090496</t>
+          <t>010-454-1089</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12584,12 +12580,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>이정춘</t>
+          <t>이우복</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>010-565-5509</t>
+          <t>010-2107-1654</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12601,25 +12597,29 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>이정춘</t>
+          <t>이우복</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01531250</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr"/>
+          <t>470102731</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>이정훈</t>
+          <t>이우복</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>53125091</t>
+          <t>010-7120-1098</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12631,64 +12631,80 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>이정훈</t>
+          <t>이우복</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>016-564-5091</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr"/>
+          <t>010-7335-8461</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>이웅재</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>100-6208-5574</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr"/>
+          <t>02-934-7067</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>이웅재</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>210-7510-5572</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr"/>
+          <t>010-4555-2991</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>이웅재</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>004-030-9581</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr"/>
+          <t>9004064150975864</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>이유</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>010-4227-9270</t>
+          <t>010-8351-4588</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -12700,25 +12716,29 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>이주하</t>
+          <t>이유</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>010-5491-9102</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>010-9826-4774</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>이진형</t>
+          <t>이유</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>010-2533-5446</t>
+          <t>010-2763-6919</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -12730,12 +12750,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>이현수</t>
+          <t>이은서</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>105-218-5801</t>
+          <t>010-4440-8951</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -12743,42 +12763,42 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>이현수</t>
+          <t>이은정</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>762-228-0108</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>30153225</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>이현옥</t>
+          <t>이은정</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>010-5207-6881</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>010-2467-7493</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이은정</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>010-6311-5570</t>
+          <t>010-2071-5849</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -12790,12 +12810,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이은정</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>010-6256-1287</t>
+          <t>010-4624-6448</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -12807,25 +12827,29 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이정우</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>010-372-2325</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>03090496</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이정우</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>010-9278-1287</t>
+          <t>120103080</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12837,72 +12861,72 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이정춘</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>121-010-6216</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
+          <t>010-565-5509</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>이정춘</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>009216187</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01531250</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>이환희</t>
+          <t>이정훈</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>010-3768-3610</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>016-564-5091</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>임것우</t>
+          <t>이정훈</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>002-581-1540</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
+          <t>53125091</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>임류경</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>010-9275-0938</t>
+          <t>010-4227-9270</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -12914,29 +12938,25 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>임류경</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>009-916-0938</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-030-9581</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>임류경</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>010-8480-3472</t>
+          <t>100-6208-5574</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -12944,46 +12964,38 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>임류경</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>010-3490-3472</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>210-7510-5572</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>임류경</t>
+          <t>이주하</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>010-2305-3472</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5491-9102</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>임상우</t>
+          <t>이진형</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>083751202</t>
+          <t>010-2533-5446</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12995,12 +13007,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>임상우</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>101-0674-5080</t>
+          <t>762-228-0108</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -13012,12 +13024,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>임채민</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>010-5917-2874</t>
+          <t>105-218-5801</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -13025,29 +13037,25 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>임호성</t>
+          <t>이현옥</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>006-294-9659</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5207-6881</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>임호성</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>010-9112-2812</t>
+          <t>010-6256-1287</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -13059,12 +13067,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>임호성</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>010-2965-2812</t>
+          <t>121-010-6216</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -13072,25 +13080,29 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>작훈인</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>010-7825-0405</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr"/>
+          <t>010-9278-1287</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>작훈인</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>010-9068-7577</t>
+          <t>009216187</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -13102,55 +13114,59 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>작훈인</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>010-5575-6485</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-372-2325</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>장대휘</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>010-4745-5142</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr"/>
+          <t>010-6311-5570</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>장서현</t>
+          <t>이환희</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>010-2639-7336</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr"/>
+          <t>010-3768-3610</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>장서현</t>
+          <t>임것우</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>010-4057-7636</t>
+          <t>002-581-1540</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -13158,25 +13174,29 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>장태양</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>003-131-0138</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr"/>
+          <t>009-916-0938</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>장태양</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>010-4693-1113</t>
+          <t>010-2305-3472</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -13188,12 +13208,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>장현준</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>984826241072</t>
+          <t>010-3490-3472</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -13205,42 +13225,42 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>장현준</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>009-848-9961</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr"/>
+          <t>010-9275-0938</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>장현준</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>180-0109-8996</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8480-3472</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>전다성</t>
+          <t>임상우</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>009447232</t>
+          <t>083751202</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -13252,12 +13272,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>전민찬</t>
+          <t>임상우</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>182-010-9727</t>
+          <t>101-0674-5080</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -13269,29 +13289,25 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>전보영</t>
+          <t>임채민</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>475-010-6202</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5917-2874</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>전보영</t>
+          <t>임호성</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>008-020-6839</t>
+          <t>006-294-9659</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -13303,42 +13319,42 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>전진우</t>
+          <t>임호성</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>070860375123028</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2965-2812</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>전진우</t>
+          <t>임호성</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>010-5303-0325</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr"/>
+          <t>010-9112-2812</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>전찬우</t>
+          <t>작훈인</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>010063437523029</t>
+          <t>010-9068-7577</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -13350,12 +13366,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>전찬우</t>
+          <t>작훈인</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>010-5303-0325</t>
+          <t>010-7825-0405</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -13363,12 +13379,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>정다고</t>
+          <t>작훈인</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>010-4757-9721</t>
+          <t>010-5575-6485</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13380,12 +13396,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>정다고</t>
+          <t>장대휘</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>010-3294-8685</t>
+          <t>010-4745-5142</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -13393,63 +13409,51 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>정다고</t>
+          <t>장서현</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>010-8951-2646</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4057-7636</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>정다운인</t>
+          <t>장서현</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>010-4325-9886</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2639-7336</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>정다운인</t>
+          <t>장태양</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>010-5220-8886</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>003-131-0138</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>정다은</t>
+          <t>장태양</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>010-4102-4804</t>
+          <t>010-4693-1113</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13461,25 +13465,29 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>정예선</t>
+          <t>장현준</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01001001001000</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>984826241072</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>정예선</t>
+          <t>장현준</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>368-981-8822</t>
+          <t>009-848-9961</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -13487,12 +13495,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>정예선</t>
+          <t>장현준</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>010-3131-0138</t>
+          <t>180-0109-8996</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13504,12 +13512,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>정예선</t>
+          <t>전다성</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>010-4693-1113</t>
+          <t>009447232</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13521,12 +13529,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>정예선</t>
+          <t>전민찬</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>010-9357-8469</t>
+          <t>182-010-9727</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13538,12 +13546,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>제과제빵</t>
+          <t>전보영</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>010-2055-6086</t>
+          <t>475-010-6202</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13555,12 +13563,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>조시련</t>
+          <t>전보영</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>010-5162-0228</t>
+          <t>008-020-6839</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -13572,29 +13580,25 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>조시련</t>
+          <t>전진우</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>010-2845-3845</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>조시련</t>
+          <t>전진우</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>010-625-1230</t>
+          <t>070860375123028</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13606,29 +13610,25 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>조예원</t>
+          <t>전찬우</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>010-9043-5274</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>조예원</t>
+          <t>전찬우</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>010-323-6505</t>
+          <t>010063437523029</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -13640,12 +13640,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>조예원</t>
+          <t>정다고</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>010-2905-6876</t>
+          <t>010-8951-2646</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13657,29 +13657,25 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>조예하</t>
+          <t>정다고</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>010-8782-5613</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3294-8685</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>조예하</t>
+          <t>정다고</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>010-9916-0369</t>
+          <t>010-4757-9721</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13691,12 +13687,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>조예하</t>
+          <t>정다운인</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>010-6210-5229</t>
+          <t>010-5220-8886</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13708,55 +13704,59 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>조예하</t>
+          <t>정다운인</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>872-567-0906</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr"/>
+          <t>010-4325-9886</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>지승환</t>
+          <t>정다은</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>010-8937-1314</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr"/>
+          <t>010-4102-4804</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>지승환</t>
+          <t>정예선</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>010-765-1744</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01001001001000</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>찬</t>
+          <t>정예선</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>006-696-3680</t>
+          <t>010-4693-1113</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -13768,25 +13768,29 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>찬</t>
+          <t>정예선</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>810-2263-3680</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr"/>
+          <t>010-9357-8469</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>천병국</t>
+          <t>정예선</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>004-730-7511</t>
+          <t>368-981-8822</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
@@ -13794,38 +13798,46 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>천병국</t>
+          <t>정예선</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>010-7622-7517</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr"/>
+          <t>010-3131-0138</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>최선을</t>
+          <t>제과제빵</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>010-873-8740</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr"/>
+          <t>010-2055-6086</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>최영이</t>
+          <t>조예원</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>010-2212-3653</t>
+          <t>010-9043-5274</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -13837,12 +13849,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>최영이</t>
+          <t>조예원</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>010-3946-5085</t>
+          <t>010-2905-6876</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -13854,12 +13866,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>최영이</t>
+          <t>조예원</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>387569798</t>
+          <t>010-323-6505</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -13871,12 +13883,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>최운새</t>
+          <t>조예하</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>010-6449-8338</t>
+          <t>010-9916-0369</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -13888,29 +13900,25 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>최운새</t>
+          <t>조예하</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>010-7154-0483</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>872-567-0906</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>최운새</t>
+          <t>조예하</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>010-4631-2868</t>
+          <t>010-8782-5613</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -13922,12 +13930,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>최원재</t>
+          <t>조예하</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>010-4677-3784</t>
+          <t>010-6210-5229</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -13939,59 +13947,55 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>최원재</t>
+          <t>지승환</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>010-3886-5085</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8937-1314</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>최이서</t>
+          <t>지승환</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>003-167-4020</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr"/>
+          <t>010-765-1744</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>하영선</t>
+          <t>찬</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>02-4010-7120</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-2263-3680</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>하영선</t>
+          <t>찬</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>010-3066-0904</t>
+          <t>006-696-3680</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14003,46 +14007,38 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>하영선</t>
+          <t>천병국</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>010-7604-5799</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-730-7511</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>하영선</t>
+          <t>천병국</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>010-6732-2782</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7622-7517</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>한기현</t>
+          <t>최선을</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>010-8865-0471</t>
+          <t>010-873-8740</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -14050,38 +14046,46 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>한기현</t>
+          <t>최영이</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>010-8602-5779</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr"/>
+          <t>010-3946-5085</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>한승진</t>
+          <t>최영이</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>100102193</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr"/>
+          <t>010-2212-3653</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>한시윤</t>
+          <t>최영이</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>002-082-9961</t>
+          <t>387569798</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14093,25 +14097,29 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>한시윤</t>
+          <t>최운새</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>010-8227-9961</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr"/>
+          <t>010-6449-8338</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>한지우산이</t>
+          <t>최운새</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>705-010-1552</t>
+          <t>010-4631-2868</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14123,12 +14131,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>한지우산이</t>
+          <t>최운새</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>801002283090</t>
+          <t>010-7154-0483</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -14140,12 +14148,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>한지우산이</t>
+          <t>최원재</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>071-987-6160</t>
+          <t>010-4677-3784</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14157,12 +14165,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>한지홍</t>
+          <t>최원재</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>010553209513</t>
+          <t>010-3886-5085</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -14174,12 +14182,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>한지홍</t>
+          <t>최이서</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>012-3671-9316</t>
+          <t>003-167-4020</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -14187,51 +14195,63 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>한지홍</t>
+          <t>하영선</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>010-9490-0951</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr"/>
+          <t>010-3066-0904</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>한지홍</t>
+          <t>하영선</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>010-7132-9316</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr"/>
+          <t>010-7604-5799</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>항공비지니스고</t>
+          <t>하영선</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>031-981-4378</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr"/>
+          <t>010-6732-2782</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>홍지원</t>
+          <t>하영선</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>010-6306-0684</t>
+          <t>02-4010-7120</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -14243,63 +14263,51 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>홍지원</t>
+          <t>한기현</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>004657010</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8602-5779</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>홍지원</t>
+          <t>한승진</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>010-4702-7909</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>100102193</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>홍지원</t>
+          <t>한시윤</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>010-3390-1991</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8227-9961</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>황도현</t>
+          <t>한시윤</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>010-546-2641</t>
+          <t>002-082-9961</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -14311,12 +14319,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>황도현</t>
+          <t>한지우산이</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>764-6560-8649</t>
+          <t>705-010-1552</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -14328,25 +14336,29 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>황현서</t>
+          <t>한지우산이</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>010-2384-4100</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr"/>
+          <t>801002283090</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>회우석</t>
+          <t>한지우산이</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>010-2502-3229</t>
+          <t>071-987-6160</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -14358,15 +14370,216 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
+          <t>한지홍</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>010-9490-0951</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>한지홍</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>010553209513</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>한지홍</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>010-7132-9316</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>한지홍</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>012-3671-9316</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>항공비지니스고</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>031-981-4378</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>홍지원</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>010-6306-0684</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>홍지원</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>010-4702-7909</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>홍지원</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>004657010</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>홍지원</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>010-3390-1991</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>황도현</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>010-546-2641</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>황도현</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>764-6560-8649</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>황현서</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>010-2384-4100</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
           <t>회우석</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>010-9457-3143</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>회우석</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>010-2502-3229</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/수강생_정밀분석_최종본.xlsx
+++ b/수강생_정밀분석_최종본.xlsx
@@ -7673,7 +7673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C441"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7696,25 +7696,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>Emal풍우고</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>033-1261-9937</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>2024343502434263230118230213</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(이름 확인필요)</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>010-5165-5152</t>
+          <t>99893569880195988958098712579898911988777498706879985112</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7726,25 +7726,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>강연경</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>010-3411-3469</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>10109653</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>강윤성</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>795-010-2529</t>
+          <t>98772339891002998220098715999884008158894799877070</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7754,125 +7758,101 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(이름 확인필요)</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>010-4423-7821</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>019-9004-5350</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>권수빈</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>010-2713-7720</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3285-5451</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>기민지</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>904-362-3919</t>
+          <t>010-5293-3318</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>(이름 확인필요)</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>810-5267-5076</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5656-1650</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>김관웅</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>010-8975-5327</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8213-0961</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(이름 확인필요)</t>
+          <t>김기현</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>010-2014-6211</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>010-8865-0471</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강지연</t>
+          <t>김다은</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>060-8744-2766</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8083-2315</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강지연</t>
+          <t>김다창</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>010-9296-4452</t>
+          <t>010-2247-2195</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7882,61 +7862,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>강지연</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>803-462-0632</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>010-8855-9990</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>고한별</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>470107373</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5368-2690</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>고한별</t>
+          <t>김도연</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>529-010-3940</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6392-9086</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>권성운</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>870-2481-0843</t>
+          <t>003-181-2003</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -7944,29 +7908,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>권성운</t>
+          <t>김명준</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>010-4909-3277</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6342-1892</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>권성운</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>916-550-8210</t>
+          <t>010-2948-0380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -7974,12 +7930,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>권수빈</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>005-195-4115</t>
+          <t>010-2196-6510</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7989,40 +7945,36 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>권수빈</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>010-3285-5451</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>010-5162-0228</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기민지</t>
+          <t>김서은</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>010-5656-1650</t>
+          <t>010-7670-2891</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>기민지</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>010-7779-0677</t>
+          <t>167937577</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -8030,42 +7982,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>기아영</t>
+          <t>김선유</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>904-706-4612</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+          <t>010-3065-3322</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>010-9522-4410</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>김관웅</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>010-5293-3318</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>김기현</t>
+          <t>김성은</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>010-8865-0471</t>
+          <t>010-9866-1616</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8075,48 +8023,32 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>김나은</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>010-4323-1315</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-9939-9315</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김소중</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>010-2933-2837</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8702-9829</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>김나은</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>003-381-0099</t>
+          <t>010-5587-3910</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8128,42 +8060,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김송익</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>010-8842-9444</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+          <t>010-9047-5710</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>010-5002-5710</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>김다은</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>010-9939-9315</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>010-8083-2315</t>
+          <t>010-7779-0677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -8171,42 +8099,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김지민</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>010-5368-2690</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>010-9260-9106</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김지우</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>010-2247-2195</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8618-3417</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>김다창</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>010-8855-9990</t>
+          <t>010-4715-6937</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8216,14 +8144,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>김도연</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>010-2058-3571</t>
+          <t>000-5911-4666</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8235,29 +8159,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김효나</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>010-4752-6297</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3477-4410</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>김도연</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>010-4260-5320</t>
+          <t>010-8470-7179</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8269,25 +8185,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>김희정</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>010-6392-9086</t>
+          <t>010-5838-0624</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>김도연</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>918-7479-8818</t>
+          <t>010-3146-0116</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -8295,42 +8207,34 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>김도연</t>
+          <t>깅은희</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>010-010-0100</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>010-6725-5155</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>김도현</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>010-2649-0101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7688-5132</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>김도현</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>010-858-5346</t>
+          <t>005-195-4115</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8342,38 +8246,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>김명준</t>
+          <t>떡</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>010-6342-1892</t>
+          <t>031-981-4378</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>김명준</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>010-2361-7882</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>512082545</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>김미</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>418-010-9648</t>
+          <t>218073646</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8385,46 +8285,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>문다빈</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>010-2897-1638</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2066-2281</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>김미</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>010-4803-0310</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4616-2481</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>문준석</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>010-3436-1638</t>
+          <t>010-8874-7107</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8434,14 +8322,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>김미</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>010-8608-6520</t>
+          <t>010-7243-6763</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -8449,72 +8333,56 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>김미</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>010010010</t>
+          <t>208-532-2306</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>김민수</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>003-181-2003</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>010-8132-8306</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>김민정</t>
+          <t>민숙경</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>010-5162-0228</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5778-3650</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>김민정</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>010-2196-6510</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>031-298-6763</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>김민정</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>010-9871-9855</t>
+          <t>010-3343-8064</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8526,76 +8394,64 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>김민정</t>
+          <t>민원기</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>010-625-1230</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8882-3026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>김민정</t>
+          <t>민준흥</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>010-2845-3845</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4374-5352</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>김민정</t>
+          <t>박서준</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>010-3123-0038</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4525-8476</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>김서은</t>
+          <t>박서후</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>010-7670-2891</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>182-010-9269</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>김서은</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>167937577</t>
+          <t>004-150-0852</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -8603,29 +8459,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>김서은</t>
+          <t>박소윤</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>010-229-9757</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5012-1461</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>김선유</t>
+          <t>박시후</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>010-3477-4410</t>
+          <t>700-4422-6602</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -8633,12 +8485,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>김선유</t>
+          <t>박어경</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>010-9522-4410</t>
+          <t>004-937-8477</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8648,31 +8500,23 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>김선희</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>181-010-5611</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7619-0025</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>김선희</t>
+          <t>박은력</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>010-5264-0738</t>
+          <t>010-3772-6360</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8682,31 +8526,23 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>김선희</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>202-010-2644</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-4405-6360</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>김성은</t>
+          <t>박재웅</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>010-9866-1616</t>
+          <t>010-3286-3005</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8716,27 +8552,23 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>김성은</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>010-3065-3322</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>105-823-3002</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>김성훈</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>02-063-1849</t>
+          <t>010-7528-0134</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -8744,46 +8576,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>박정진</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>010-2643-3860</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8458-1321</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>김성훈</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>643-010-9518</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>008-748-7321</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>박지승</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>280102590</t>
+          <t>232-010-4204</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8795,29 +8615,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>박찬화</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>010-2337-2197</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6763-3954</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>김소연</t>
+          <t>박하는</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>010-9411-5494</t>
+          <t>004135124</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8827,48 +8643,36 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>김소연</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>438531116</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3042-6365</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>김소연</t>
+          <t>방뢔리아</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>010-3192-4180</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>00010010000000</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>김소중</t>
+          <t>백수열</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>010-8702-9829</t>
+          <t>01001001001001000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -8876,12 +8680,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>김소중</t>
+          <t>서아론</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>010-2948-0380</t>
+          <t>005-346-4576</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -8889,12 +8693,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>김송익</t>
+          <t>세종요리제과기술학원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>010-9047-5710</t>
+          <t>031-986-1933</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -8902,97 +8706,69 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>김송익</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>010-5002-5710</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>904-480-3821</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>김수민</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>010-5587-3910</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2751-8260</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>김예빈</t>
+          <t>손진형</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>010-8372-3369</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>110-3896-1169</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>김예빈</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>010-4451-9576</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8729-5933</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>김용민</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>463-010-3420</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01000010010010010</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>김용민</t>
+          <t>송하린</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0010302382900</t>
+          <t>010259338</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9004,97 +8780,65 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>김유정</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>002-443-0554</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6390-7152</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>김유정</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>010-9297-4166</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2447-2733</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>김유정</t>
+          <t>신지응</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>010-2323-4517</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>108-325-9659</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>김재민</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>010-228-4722</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5136-9658</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>김재민</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>010-4908-3421</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2088-4787</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>김재민</t>
+          <t>안건하다</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>010-3340-3421</t>
+          <t>005689040</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9106,12 +8850,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>김재훈일시</t>
+          <t>안세은</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>010-5851-2600</t>
+          <t>006-818-3587</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9123,12 +8867,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>김재훈일시</t>
+          <t>안시우</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>010-7705-3658</t>
+          <t>636121922</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9138,31 +8882,19 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>김재훈일시</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>010-3424-8456</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-0321-2799</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>김주승</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>210-4083-4285</t>
+          <t>010-239-2903</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9174,12 +8906,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>김주승</t>
+          <t>양재준</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>010-8595-4112</t>
+          <t>901603211</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9189,61 +8921,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>김주승</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>010-4057-7636</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>016-564-5091</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>김지민</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>010-9260-9106</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>903-211-1285</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>김지우</t>
+          <t>양정인</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>010-8618-3417</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>010-264-3088</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>010-4715-6937</t>
+          <t>010-3798-3144</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -9255,12 +8971,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>김하은</t>
+          <t>여민욱</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>000-5911-4666</t>
+          <t>010-3337-6745</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9270,14 +8986,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>김효나</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>010-8213-0961</t>
+          <t>010-3319-0845</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -9285,12 +8997,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>김효나</t>
+          <t>여승원</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>010-8470-7179</t>
+          <t>010527747270026111360</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9300,14 +9012,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>김희정</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>010-5838-0624</t>
+          <t>010-372-2325</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -9315,25 +9023,21 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>김희정</t>
+          <t>염지웅</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>010-3146-0116</t>
+          <t>810-3982-4645</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>깅은희</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>010-6725-5155</t>
+          <t>010-6351-1537</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9345,25 +9049,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>깅은희</t>
+          <t>오먼걸</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>010-7688-5132</t>
+          <t>600-335-2681</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>남이정</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>010-5120-8254</t>
+          <t>904-706-4612</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9375,12 +9075,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>오지원</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>010-3923-4450</t>
+          <t>610-8580-3486</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9390,14 +9090,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>남이정</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>010-5915-4450</t>
+          <t>010-7622-9381</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9409,29 +9105,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>남이정</t>
+          <t>왕성지</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>010-7321-5702</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8988-0556</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>남이정</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>010-4118-0184</t>
+          <t>910990847</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9443,25 +9131,29 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>왕옹유</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>02-547-5233</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>120102529</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>운승혁</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>052-714-8429</t>
+          <t>004491365</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9473,25 +9165,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>동광역집쌀유</t>
+          <t>위묘한</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>031-606-3003</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>010-8750-8992</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>유리</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>693-010-2346</t>
+          <t>010-2834-3924</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9501,14 +9197,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>떡</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>02-0542-01720</t>
+          <t>010-5458-5770</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9520,63 +9212,51 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>유민지</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>008-654-7364</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6263-0556</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>유용우</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>512082545</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>200-2752-8294</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>유원민</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>218073646</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010010010</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>유진성</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>010-5212-6755</t>
+          <t>092617358</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9586,40 +9266,40 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>문다빈</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>010-4616-2481</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>005-161-8958</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>문다빈</t>
+          <t>윤수한</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>010-4374-5352</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>010-3186-9381</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>문준석</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>010-8874-7107</t>
+          <t>010-9278-1287</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9631,55 +9311,51 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>윤진우</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>010-8217-0042</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>010-565-5509</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>민경령</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>010-9217-0042</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>448434687</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>민경령</t>
+          <t>윤희라</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>010-8132-8306</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5491-9102</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>민경령</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>208-532-2306</t>
+          <t>009-980-2112</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -9687,25 +9363,21 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>의재의</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>031-298-6763</t>
+          <t>120104112</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>민숙경</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>010-7243-6763</t>
+          <t>808-482-6377</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -9713,12 +9385,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>이경희</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>010-3343-8064</t>
+          <t>010-5611-0822</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9730,12 +9402,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>민원기</t>
+          <t>이금비</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>010-5778-3650</t>
+          <t>010-7337-0882</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -9743,55 +9415,51 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>민준흥</t>
+          <t>이나경</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>010-8882-3026</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>010176443878</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>박서준</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>004-937-8477</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7735-0405</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>박서준</t>
+          <t>이동은</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>010-4525-8476</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>010-2456-0685</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>박서후</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>182-010-9269</t>
+          <t>010-8727-6539</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9803,12 +9471,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>박성현</t>
+          <t>이든지</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>010-3496-4008</t>
+          <t>010-9600-0012</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9818,14 +9486,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>박성화</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>010-5320-8634</t>
+          <t>010-8443-1396</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9837,29 +9501,21 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>박성화</t>
+          <t>이상혁</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>010-4671-8633</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4706-9331</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>박성화</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>636-484-2665</t>
+          <t>010-7933-9331</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -9867,12 +9523,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>박어경</t>
+          <t>이서연</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>010-7619-0025</t>
+          <t>010010010010010010</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -9880,12 +9536,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>박어경</t>
+          <t>이성윤</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>058200026</t>
+          <t>802-071-6548</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9895,27 +9551,19 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>박은력</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>810-4405-6360</t>
+          <t>210-2357-0197</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>박은력</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>010-3772-6360</t>
+          <t>010-5029-8270</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9927,29 +9575,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>박이소</t>
+          <t>이소미</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>010-6328-2348</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5438-5194</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>박이소</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>010-3688-5475</t>
+          <t>010-963-2501</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9961,68 +9601,68 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>박재웅</t>
+          <t>이송연</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>010-2088-4787</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>008649064</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>박재웅</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>010-3286-3005</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-036-2289</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>박정진</t>
+          <t>이수경</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>010-8458-1321</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
+          <t>010-4046-3924</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>박정진</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>008-748-7321</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>010-9379-3486</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>박지승</t>
+          <t>이수호</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>004-150-0852</t>
+          <t>005-450-9186</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -10030,89 +9670,77 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>박하는</t>
+          <t>이승수양</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>010-3042-6365</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>010-4344-5525</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>박하는</t>
+          <t>이승준</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>004135124</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8442-8651</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>박하람</t>
-        </is>
-      </c>
+      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>010-8236-6094</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5917-2874</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>박하람</t>
+          <t>이승환</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>010-392-6094</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
+          <t>004-769-6662</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>010-9889-6539</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>박하랑</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>010-6763-3954</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>박행님</t>
+          <t>이아영</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>010-1290-4454</t>
+          <t>010-4716-4612</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10124,12 +9752,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>박행님</t>
+          <t>이아인</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>010-3619-0021</t>
+          <t>010-9918-5123</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10141,29 +9769,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>이은서</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>158-010-4355</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4440-8951</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>이정우</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>010-3123-8001</t>
+          <t>120103080</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10173,14 +9797,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>방뢔리아</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>00010010000000</t>
+          <t>010-3140-8826</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -10188,46 +9808,34 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>방뢔리아</t>
+          <t>이정춘</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>010-5296-7701</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>003-008-1295</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>방뢔리아</t>
-        </is>
-      </c>
+      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0189691682433042</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>01531250</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>이정훈</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>010-2042-6369</t>
+          <t>75908465</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10237,14 +9845,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>배해란</t>
-        </is>
-      </c>
+      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>383-010-9249</t>
+          <t>53125091</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10256,12 +9860,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>배해란</t>
+          <t>이진형</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>010-3092-5988</t>
+          <t>003-562-4517</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10271,14 +9875,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>배해란</t>
-        </is>
-      </c>
+      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>010-8223-3092</t>
+          <t>010-2533-5446</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10290,12 +9890,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>010-2633-3685</t>
+          <t>010-3490-3472</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10305,31 +9905,23 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>백수열</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>010-9461-4643</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>105-218-5801</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>이현옥</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>945782420115</t>
+          <t>010-8627-8972</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10341,38 +9933,38 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>이현지</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>459-845-5310</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>009216187</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>백수열</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01001001001001000</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>03090496</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>서아론</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>005-346-4576</t>
+          <t>121-010-6216</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -10380,81 +9972,73 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>서아론</t>
+          <t>이환희</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>010-5646-5801</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
+          <t>010-3768-3610</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>세종요리제과기술학원</t>
+          <t>임것우</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>031-986-1933</t>
+          <t>002-581-1540</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>손견호</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>010259338</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5448-9196</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>임류경</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>904-480-3821</t>
+          <t>010-8480-3472</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>손견호</t>
-        </is>
-      </c>
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>010-2751-8260</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>010-2305-3472</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>손견호</t>
-        </is>
-      </c>
+      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>801094618260</t>
+          <t>009-916-0938</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10466,25 +10050,25 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>손진형</t>
+          <t>임상우</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>110-3896-1169</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>101-0674-5080</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>송지후</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>210-8375-3274</t>
+          <t>008-532-1360</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10494,61 +10078,49 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>송지후</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01000010010010010</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr"/>
+          <t>083751202</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>임채민</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>87549457</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>008-489-9717</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>송지후</t>
+          <t>장대휘</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>010-3887-3274</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7622-7517</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>송하린</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>010-8729-5933</t>
+          <t>010-4745-5142</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -10556,29 +10128,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>승손에요</t>
+          <t>장서현</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>010-2540-5528</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2639-7336</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>승손에요</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>010-9138-7130</t>
+          <t>010063437523029</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10590,42 +10154,34 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>승손에요</t>
+          <t>장태양</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>010-0428-7130</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
+          <t>003-131-0138</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>010-4693-1113</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>신구호</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>010-2447-2733</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-    </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>신구호</t>
-        </is>
-      </c>
+      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>010-6390-7152</t>
+          <t>010-873-8740</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -10633,64 +10189,72 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>장현준</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>010-7202-7169</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
+          <t>010-4102-4804</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>신구호</t>
-        </is>
-      </c>
+      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>004-187-2733</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
+          <t>180-0109-8996</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>신지응</t>
-        </is>
-      </c>
+      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>108-325-9659</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>984826241072</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>신지응</t>
+          <t>전다성</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>010-5136-9658</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
+          <t>009447232</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>전민찬</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>010-5240-3831</t>
+          <t>182-010-9727</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10702,46 +10266,34 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>전진우</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>001-517-6315</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>신학림</t>
+          <t>전찬우</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>09876670</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>신혁진</t>
-        </is>
-      </c>
+      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>835-010-2364</t>
+          <t>070860375123028</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10753,12 +10305,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>제과제빵</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>504-010-5241</t>
+          <t>010-2055-6086</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10770,63 +10322,47 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>지승환</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>010-2100-6423</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8937-1314</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>신혁진</t>
+          <t>찬</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>010-4740-6511</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-2263-3680</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>아비지</t>
-        </is>
-      </c>
+      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10109653</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-0108-0556</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>안건하다</t>
+          <t>천병국</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>010176443878</t>
+          <t>010-765-1744</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -10836,48 +10372,36 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>안건하다</t>
-        </is>
-      </c>
+      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>005689040</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-730-7511</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>안세은</t>
+          <t>최선을</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>006-818-3587</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8875-1310</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>최이서</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>010-0321-2799</t>
+          <t>003-167-4020</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -10885,46 +10409,34 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>한기현</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>636121922</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8602-5779</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>한승진</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>010-239-2903</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>012-3671-9316</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>양재준</t>
-        </is>
-      </c>
+      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>003-008-1295</t>
+          <t>100102193</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -10932,76 +10444,60 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>양재준</t>
+          <t>한시윤</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>901603211</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8227-9961</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>양정인</t>
+          <t>한지홍</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>010-8443-1396</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
+          <t>010-9490-0951</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>010-7132-9316</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>010553209513</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>양정인</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>010-3798-3144</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>여민욱</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>010-3319-0845</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>여민욱</t>
+          <t>황도현</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>010-3337-6745</t>
+          <t>764-6560-8649</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11011,14 +10507,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>여승원</t>
-        </is>
-      </c>
+      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>010527747270026111360</t>
+          <t>010-546-2641</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11030,3556 +10522,15 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>여승원</t>
+          <t>황현서</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>008-532-1360</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>염지웅</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>010-6351-1537</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>염지웅</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>810-3982-4645</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>오먼걸</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>004-036-2289</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>오지원</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>610-8580-3486</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>오지원</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>010-9379-3486</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>왕다영</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>010-8365-0471</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>왕다영</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>900-7312-7844</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>왕다영</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>010-4362-3019</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>왕성지</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>910990847</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>왕옹유</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>010-3140-8826</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>왕옹유</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>120102529</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>운승혁</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>010-2066-2281</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>운승혁</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>004491365</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>위묘한</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>010-8627-8972</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>위묘한</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>010-8750-8992</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>위요한</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>010-8627-8972</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>위요한</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>010-8750-8992</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>위요한</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>010-3763-3610</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>유나오가스유나영강</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>010-5207-6881</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>유나오가스유나영강</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>010-2367-4628</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>유나오가스유나영강</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>643-010-3750</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>유나오가스유나영강</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>010-9600-0012</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>유리</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>010-5611-0822</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>유리</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>010-5458-5770</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>유민지</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>010-0108-0556</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>유민지</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>010-6263-0556</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>유민지</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>010-8988-0556</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>유용우</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>200-2752-8294</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>773-866-8766</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>605-010-3821</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>807-010-8322</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>17266727</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>010010010</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>유진성</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>005-161-8958</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>유진성</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>010-5380-0978</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>유태한</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>008-489-9717</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>윤수한</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>010-3186-9381</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>윤수한</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>010-7622-9381</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>윤종호</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>475789276</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>윤종호</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>010-2384-2350</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>윤종호</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>010-8208-9269</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>윤진우</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>684464689</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>윤진우</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>448434687</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>윤희라</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>009-980-2112</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>의재의</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>120104112</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>이경희</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>010-2008-6384</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>이금비</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>208-710-4252</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>이금비</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>010-7337-0882</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>이금비</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>010-2828-0171</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>이금비</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>010-4663-2519</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>이나경</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>010-7735-0405</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>이나경</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>75908465</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>이다운</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>010-9008-9392</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>이다운</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>690106361</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>이다운</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>010-4475-5834</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>이다운</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>010-6404-5266</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>이다정</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>890-0843-6858</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>이다정</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>004-306-3028</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>이다정</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>010-8930-1658</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>이다정</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>010-2767-0893</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>이동은</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>010-2456-0685</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>이동은</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>092617358</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>이든지</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>010-3970-6405</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>이든지</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>010-2455-8443</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>이든지</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>010-9600-0012</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>이민지대시</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>010-2057-0087</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>이민지대시</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>010-9974-3970</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>이민지대시</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>006-894-1641</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>이방상</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>010-5612-4249</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>이방상</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>010-9472-9371</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>이방상</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>010-8614-8745</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>이상혁</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>010-4706-9331</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>777315248</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>010010010010010010</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>092-010-2744</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>333-010-2490</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>이서연</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>861-010-6226</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>이소미</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>808-482-6377</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>이소미</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>010-963-2501</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>이송연</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>008649064</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>이수경</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>010-4046-3924</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>이수경</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>010-2834-3924</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>이수아</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>010-264-3088</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>이수호</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>005-450-9186</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>이수호</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>010-5448-9196</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>이승수양</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>010-4344-5525</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>이승준</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>010-3381-8651</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>이승준</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>010-8442-8651</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>이승환</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>010-9889-6539</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>이승환</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>003-562-4517</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>이승환</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>004-769-6662</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>이승환</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>010-8727-6539</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>이아영</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>010-4716-4612</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>이아인</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>010-9918-5123</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>이예영</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>010-9496-2605</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>이예영</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>010-2832-5092</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>이예영</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>010-454-1089</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>이우복</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>010-2107-1654</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>이우복</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>470102731</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>이우복</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>010-7120-1098</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>이우복</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>010-7335-8461</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>이웅재</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>02-934-7067</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>이웅재</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>010-4555-2991</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>이웅재</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>9004064150975864</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>이유</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>010-8351-4588</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>이유</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>010-9826-4774</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>이유</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>010-2763-6919</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>이은서</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>010-4440-8951</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>이은정</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>30153225</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>이은정</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>010-2467-7493</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>이은정</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>010-2071-5849</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>이은정</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>010-4624-6448</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>이정우</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>03090496</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>이정우</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>120103080</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>이정춘</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>010-565-5509</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>이정춘</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>01531250</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>이정훈</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>016-564-5091</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>이정훈</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>53125091</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>이정희</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>010-4227-9270</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>이정희</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>004-030-9581</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>이정희</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>100-6208-5574</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>이정희</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>210-7510-5572</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>이주하</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>010-5491-9102</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>이진형</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>010-2533-5446</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>이현수</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>762-228-0108</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>이현수</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>105-218-5801</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>이현옥</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>010-5207-6881</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>010-6256-1287</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>121-010-6216</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>010-9278-1287</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>009216187</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>010-372-2325</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>이현지</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>010-6311-5570</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>이환희</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>010-3768-3610</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>임것우</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>002-581-1540</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>009-916-0938</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>010-2305-3472</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>010-3490-3472</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>010-9275-0938</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>010-8480-3472</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>임상우</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>083751202</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>임상우</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>101-0674-5080</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>임채민</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>010-5917-2874</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>임호성</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>006-294-9659</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>임호성</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>010-2965-2812</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>임호성</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>010-9112-2812</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>작훈인</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>010-9068-7577</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>작훈인</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>010-7825-0405</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>작훈인</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>010-5575-6485</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>장대휘</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>010-4745-5142</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>장서현</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>010-4057-7636</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>장서현</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>010-2639-7336</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>장태양</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>003-131-0138</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>장태양</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>010-4693-1113</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>장현준</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>984826241072</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>장현준</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>009-848-9961</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>장현준</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>180-0109-8996</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>전다성</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>009447232</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>전민찬</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>182-010-9727</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>전보영</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>475-010-6202</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>전보영</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>008-020-6839</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>전진우</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>010-5303-0325</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>전진우</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>070860375123028</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>전찬우</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>010-5303-0325</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>전찬우</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>010063437523029</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>정다고</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>010-8951-2646</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>정다고</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>010-3294-8685</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>정다고</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>010-4757-9721</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>정다운인</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>010-5220-8886</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>정다운인</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>010-4325-9886</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>정다은</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>010-4102-4804</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>정예선</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>01001001001000</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>정예선</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>010-4693-1113</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>정예선</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>010-9357-8469</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>정예선</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>368-981-8822</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr"/>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>정예선</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>010-3131-0138</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>제과제빵</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>010-2055-6086</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>조예원</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>010-9043-5274</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>조예원</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>010-2905-6876</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>조예원</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>010-323-6505</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>조예하</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>010-9916-0369</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>조예하</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>872-567-0906</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>조예하</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>010-8782-5613</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>조예하</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>010-6210-5229</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>지승환</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>010-8937-1314</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>지승환</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>010-765-1744</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>찬</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>810-2263-3680</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>찬</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>006-696-3680</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>천병국</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>004-730-7511</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>천병국</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>010-7622-7517</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>최선을</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>010-873-8740</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>최영이</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>010-3946-5085</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>최영이</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>010-2212-3653</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>최영이</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>387569798</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>최운새</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>010-6449-8338</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>최운새</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>010-4631-2868</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>최운새</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>010-7154-0483</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>최원재</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>010-4677-3784</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>최원재</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>010-3886-5085</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>최이서</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>003-167-4020</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>하영선</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>010-3066-0904</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>하영선</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>010-7604-5799</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>하영선</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>010-6732-2782</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>하영선</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>02-4010-7120</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>한기현</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>010-8602-5779</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>한승진</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>100102193</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>한시윤</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>010-8227-9961</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>한시윤</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>002-082-9961</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>한지우산이</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>705-010-1552</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>한지우산이</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>801002283090</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>한지우산이</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>071-987-6160</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>한지홍</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>010-9490-0951</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>한지홍</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>010553209513</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>한지홍</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>010-7132-9316</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>한지홍</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>012-3671-9316</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>항공비지니스고</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>031-981-4378</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>홍지원</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>010-6306-0684</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>홍지원</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>010-4702-7909</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>홍지원</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>004657010</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>홍지원</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>010-3390-1991</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>황도현</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>010-546-2641</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>황도현</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>764-6560-8649</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>황현서</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
           <t>010-2384-4100</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>회우석</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>010-9457-3143</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr"/>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>회우석</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>010-2502-3229</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/수강생_정밀분석_최종본.xlsx
+++ b/수강생_정밀분석_최종본.xlsx
@@ -7673,7 +7673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7696,12 +7696,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Emal풍우고</t>
+          <t>Emal불로증</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024343502434263230118230213</t>
+          <t>323230118230213</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7714,24 +7714,20 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2024345024346</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>99893569880195988958098712579898911988777498706879985112</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>강연경</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10109653</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7743,12 +7739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강윤성</t>
+          <t>강연경</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98772339891002998220098715999884008158894799877070</t>
+          <t>10109653</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7758,10 +7754,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>권수빈</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>019-9004-5350</t>
+          <t>010-3285-5451</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -7769,34 +7769,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>권수빈</t>
+          <t>기민지</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>010-3285-5451</t>
+          <t>010-5293-3318</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>기민지</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>010-5293-3318</t>
+          <t>010-5656-1650</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>김관웅</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>010-5656-1650</t>
+          <t>010-8213-0961</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -7804,22 +7804,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>김관웅</t>
+          <t>김기현</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>010-8213-0961</t>
+          <t>010-8602-5779</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>김기현</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>010-8865-0471</t>
@@ -7891,7 +7887,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>010-6392-9086</t>
+          <t>003-181-2003</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -7900,7 +7896,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>003-181-2003</t>
+          <t>010-6392-9086</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -7935,7 +7931,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>010-2196-6510</t>
+          <t>010-5162-0228</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7948,7 +7944,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>010-5162-0228</t>
+          <t>010-2196-6510</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7971,20 +7967,24 @@
       <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>김선유</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>167937577</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>010-9522-4410</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>김선유</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>010-3065-3322</t>
@@ -7993,10 +7993,14 @@
       <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>김성은</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>010-9522-4410</t>
+          <t>010-9866-1616</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8006,135 +8010,131 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>김성은</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>010-9866-1616</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+          <t>010-9939-9315</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>김소중</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>010-8702-9829</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>010-5587-3910</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>010-9939-9315</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>김소중</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>010-8702-9829</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>김송익</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>010-5587-3910</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+          <t>010-9047-5710</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>010-5002-5710</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>김송익</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>010-9047-5710</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>김수민</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>010-5002-5710</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7779-0677</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>김지민</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>010-7779-0677</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>010-9260-9106</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>김지민</t>
+          <t>김지우</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>010-9260-9106</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8618-3417</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>김지우</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>010-8618-3417</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>010-4715-6937</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>010-4715-6937</t>
+          <t>000-5911-4666</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8144,153 +8144,153 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>김효나</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>000-5911-4666</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+          <t>010-3477-4410</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>010-8470-7179</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>김효나</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>010-3477-4410</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>김희정</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>010-8470-7179</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+          <t>010-3146-0116</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>010-5838-0624</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>깅은희</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>010-6725-5155</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>김희정</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>010-5838-0624</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>010-3146-0116</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-    </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>깅은희</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>010-6725-5155</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7688-5132</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>010-7688-5132</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>005-195-4115</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>떡</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>005-195-4115</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>031-981-4378</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>떡</t>
+          <t>떡쩌EmallEmalil</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>031-981-4378</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>218073646512082545</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>문다빈</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>512082545</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-2066-2281</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>218073646</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4616-2481</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>문다빈</t>
+          <t>민경령</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>010-2066-2281</t>
+          <t>208-532-2306</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -8299,20 +8299,24 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>010-4616-2481</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>010-8132-8306</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>문준석</t>
+          <t>민숙경</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>010-8874-7107</t>
+          <t>010-3343-8064</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8325,64 +8329,68 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>010-7243-6763</t>
+          <t>010-5778-3650</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>민경령</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>208-532-2306</t>
+          <t>031-298-6763</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>민원기</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>010-8132-8306</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8882-3026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>민숙경</t>
+          <t>민준흥</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>010-5778-3650</t>
+          <t>010-4374-5352</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>박서준</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>031-298-6763</t>
+          <t>010-4525-8476</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>박서후</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>010-3343-8064</t>
+          <t>182-010-9269</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8392,14 +8400,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>민원기</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>010-8882-3026</t>
+          <t>004-150-0852</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -8407,12 +8411,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>민준흥</t>
+          <t>박소윤</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>010-4374-5352</t>
+          <t>010-5012-1461</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -8420,12 +8424,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>박서준</t>
+          <t>박시후</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>010-4525-8476</t>
+          <t>700-4422-6602</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -8433,12 +8437,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>박서후</t>
+          <t>박어경</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>182-010-9269</t>
+          <t>004-937-8477</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8448,23 +8452,27 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>박은력</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>004-150-0852</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>010-3772-6360</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>박소윤</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>010-5012-1461</t>
+          <t>810-4405-6360</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -8472,25 +8480,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>박시후</t>
+          <t>박재웅HP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>700-4422-6602</t>
+          <t>010-7528-0134</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>박어경</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>004-937-8477</t>
+          <t>105-823-3002</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8503,33 +8507,33 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>010-7619-0025</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>010-3286-3005</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>박은력</t>
+          <t>박정진HP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>010-3772-6360</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-8458-1321</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>810-4405-6360</t>
+          <t>008-748-7321</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -8537,12 +8541,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>박재웅</t>
+          <t>박지승</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>010-3286-3005</t>
+          <t>232-010-4204</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8552,45 +8556,53 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>박찬화HPe</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>105-823-3002</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
+          <t>010-6763-3954</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>박하는</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>004135124</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>010-7528-0134</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-    </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>박정진</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>010-8458-1321</t>
+          <t>010-3042-6365</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>방뢔리아</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>008-748-7321</t>
+          <t>00010010000000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -8598,29 +8610,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>박지승</t>
+          <t>서아론</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>232-010-4204</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>005-346-4576</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>박찬화</t>
+          <t>세종요리제과기술학원</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>010-6763-3954</t>
+          <t>031-986-1933</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -8628,12 +8636,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>박하는</t>
+          <t>손견호</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>004135124</t>
+          <t>801094618260</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8646,20 +8654,16 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>010-3042-6365</t>
+          <t>904-480-3821</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>방뢔리아</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>00010010000000</t>
+          <t>010-2751-8260</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -8667,25 +8671,21 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>백수열</t>
+          <t>손진형</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01001001001001000</t>
+          <t>010-8729-5933</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>서아론</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>005-346-4576</t>
+          <t>110-3896-1169</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -8693,25 +8693,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>세종요리제과기술학원</t>
+          <t>송하린</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>031-986-1933</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>010259338</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>손견호</t>
+          <t>신구호</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>904-480-3821</t>
+          <t>010-2447-2733</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -8720,7 +8724,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>010-2751-8260</t>
+          <t>010-6390-7152</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -8728,12 +8732,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>손진형</t>
+          <t>신지응</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>110-3896-1169</t>
+          <t>108-325-9659</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -8742,20 +8746,16 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>010-8729-5933</t>
+          <t>010-5136-9658</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>송지후</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01000010010010010</t>
+          <t>010-2088-4787</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -8763,12 +8763,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>송하린</t>
+          <t>안건하다HP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>010259338</t>
+          <t>005689040</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8780,65 +8780,77 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>신구호</t>
+          <t>안세은HP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>010-6390-7152</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>006-818-3587</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>안시우</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>010-2447-2733</t>
+          <t>010-0321-2799</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>신지응</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>108-325-9659</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>636121922</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>010-5136-9658</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>010-239-2903</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>양재준</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>010-2088-4787</t>
+          <t>016-564-5091</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>안건하다</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>005689040</t>
+          <t>901603211</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8848,31 +8860,23 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>안세은</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>006-818-3587</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>903-211-1285</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>안시우</t>
+          <t>양정인</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>636121922</t>
+          <t>010-264-3088</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8885,16 +8889,24 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>010-0321-2799</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>010-3798-3144</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>여민욱</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>010-239-2903</t>
+          <t>010-3337-6745</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8906,12 +8918,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>양재준</t>
+          <t>여승원</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>901603211</t>
+          <t>010527747270026111360</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8921,10 +8933,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>염지웅</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>016-564-5091</t>
+          <t>810-3982-4645</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -8933,111 +8949,127 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>903-211-1285</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>010-6351-1537</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>양정인</t>
+          <t>오먼걸</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>010-264-3088</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
+          <t>600-335-2681</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>오지원이지만</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>610-8580-3486</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>010-3798-3144</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>010-7622-9381</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>여민욱</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>010-3337-6745</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>왕성지</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>010-8988-0556</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>910990847</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>010-3319-0845</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>여승원</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>010527747270026111360</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>왕옹유</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>120102529</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>010-372-2325</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>염지웅</t>
+          <t>위묘한</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>810-3982-4645</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>010-8750-8992</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>유리이하윤</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>010-6351-1537</t>
+          <t>010-2834-3924</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9047,79 +9079,75 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>오먼걸</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>600-335-2681</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>010-5458-5770</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>유민지</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>904-706-4612</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6263-0556</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>오지원</t>
+          <t>유민지HP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>610-8580-3486</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-0108-0556</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>010-7622-9381</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-6263-0556</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>왕성지</t>
+          <t>유용우</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>010-8988-0556</t>
+          <t>200-2752-8294</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>유진성</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>910990847</t>
+          <t>092617358</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9129,14 +9157,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>왕옹유</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>120102529</t>
+          <t>005-161-8958</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9148,12 +9172,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>운승혁</t>
+          <t>윤수한안건하</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>004491365</t>
+          <t>010-3186-9381</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9163,14 +9187,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>위묘한</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>010-8750-8992</t>
+          <t>010-9278-1287</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9182,12 +9202,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>유리</t>
+          <t>윤진우</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>010-2834-3924</t>
+          <t>448434687</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9200,7 +9220,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>010-5458-5770</t>
+          <t>010-565-5509</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9212,12 +9232,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>유민지</t>
+          <t>윤희라</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>010-6263-0556</t>
+          <t>009-980-2112</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -9225,25 +9245,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>유용우</t>
+          <t>의재의</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>200-2752-8294</t>
+          <t>120104112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>유원민</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>010010010</t>
+          <t>808-482-6377</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -9251,12 +9267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>유진성</t>
+          <t>이경희이지인</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>092617358</t>
+          <t>010-5611-0822</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9266,27 +9282,23 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>이나경HP</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>005-161-8958</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-7735-0405</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>윤수한</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>010-3186-9381</t>
+          <t>010176443878</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9299,7 +9311,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>010-9278-1287</t>
+          <t>75908465</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9311,12 +9323,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>윤진우</t>
+          <t>이동은</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>010-565-5509</t>
+          <t>010-8727-6539</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9329,7 +9341,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>448434687</t>
+          <t>010-2456-0685</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9341,34 +9353,42 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>윤희라</t>
+          <t>이든지이수빈</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>010-5491-9102</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>010-8443-1396</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>009-980-2112</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>010-9600-0012</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>의재의</t>
+          <t>이상혁HP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>120104112</t>
+          <t>010-4706-9331</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -9377,7 +9397,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>808-482-6377</t>
+          <t>010-7933-9331</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -9385,111 +9405,99 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>이경희</t>
+          <t>이성윤Moble</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>010-5611-0822</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
+          <t>210-2357-0197</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>010-5029-8270</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>이금비</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>802-071-6548</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>이소미</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>010-963-2501</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>010-5438-5194</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>이소지임지영이어진이금비안에서</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
         <is>
           <t>010-7337-0882</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>이나경</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>010176443878</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>010-7735-0405</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>이동은</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>010-2456-0685</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>010-8727-6539</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>이든지</t>
+          <t>이송연H</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>010-9600-0012</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>004-036-2289</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>010-8443-1396</t>
+          <t>008649064</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9501,34 +9509,42 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>이상혁</t>
+          <t>이수경이경진</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>010-4706-9331</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>010-9379-3486</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>010-7933-9331</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>010-4046-3924</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>이서연</t>
+          <t>이수아</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>010010010010010010</t>
+          <t>010-3768-3610</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -9536,116 +9552,120 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>이성윤</t>
+          <t>이수호</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>802-071-6548</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
+          <t>005-450-9186</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>이승수양HP</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>010-4344-5525</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>210-2357-0197</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
-    </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>이승준</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>010-5029-8270</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
+          <t>010-5917-2874</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>010-8442-8651</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>이승환</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>010-9889-6539</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>이소미</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>010-5438-5194</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>010-963-2501</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>004-769-6662</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>이아영</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>904-706-4612</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>이송연</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>008649064</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>010-4716-4612</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>004-036-2289</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>이수경</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>010-4046-3924</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>이아인</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>010-9379-3486</t>
+          <t>010-9918-5123</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9657,12 +9677,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>이수호</t>
+          <t>이은서HP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>005-450-9186</t>
+          <t>010-4440-8951</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -9670,60 +9690,60 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>이승수양</t>
+          <t>이정우</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>010-4344-5525</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
+          <t>010-3140-8826</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>120103080</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>이승준</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>010-8442-8651</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
-    </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>이정춘</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>010-5917-2874</t>
+          <t>003-008-1295</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>이승환</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>004-769-6662</t>
+          <t>01531250</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>이정훈</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>010-9889-6539</t>
+          <t>53125091</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9735,107 +9755,103 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>이아영</t>
+          <t>이주하HP</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>010-4716-4612</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5491-9102</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>이아인</t>
+          <t>이진형HP</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>010-9918-5123</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
+          <t>010-2533-5446</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>003-562-4517</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>이은서</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>010-4440-8951</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>이정우</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>120103080</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>105-218-5801</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>010-3140-8826</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>010-3490-3472</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>이정춘</t>
+          <t>이현옥</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>003-008-1295</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>010-8627-8972</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>이현지</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01531250</t>
+          <t>121-010-6216</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>이정훈</t>
-        </is>
-      </c>
+      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>75908465</t>
+          <t>009216187</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9848,7 +9864,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>53125091</t>
+          <t>03090496</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9860,12 +9876,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>이진형</t>
+          <t>이현지HP</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>003-562-4517</t>
+          <t>010-6311-5570</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9878,24 +9894,20 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>010-2533-5446</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-372-2325</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>이현수</t>
+          <t>이현지유현우</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>010-3490-3472</t>
+          <t>010-2455-8443</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9908,76 +9920,72 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>105-218-5801</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>010-6256-1287</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>이현옥</t>
+          <t>이환희</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>010-8627-8972</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-3458-5397</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>이현지</t>
+          <t>임것우</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>009216187</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5448-9196</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>03090496</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
+          <t>002-581-1540</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>임류경</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>010-2305-3472</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr"/>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>121-010-6216</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
-    </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>이환희</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>010-3768-3610</t>
+          <t>009-916-0938</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9987,45 +9995,49 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>임것우</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>002-581-1540</t>
+          <t>010-8480-3472</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>임상우</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>010-5448-9196</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>008-532-1360</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>임류경</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>010-8480-3472</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>101-0674-5080</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>010-2305-3472</t>
+          <t>083751202</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10035,83 +10047,79 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>임채민</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>009-916-0938</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>008-489-9717</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>임상우</t>
+          <t>장대휘HP</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>101-0674-5080</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-4745-5142</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>008-532-1360</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
+          <t>010-7622-7517</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>장서현HP</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>010-2639-7336</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>083751202</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>010063437523029</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
         <is>
           <t>부모</t>
         </is>
       </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>임채민</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>008-489-9717</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>장대휘</t>
+          <t>장태양</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>010-7622-7517</t>
+          <t>010-873-8740</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -10120,29 +10128,33 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>010-4745-5142</t>
+          <t>003-131-0138</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>장서현</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>010-2639-7336</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
+          <t>010-4693-1113</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>장현준</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>010063437523029</t>
+          <t>010-4102-4804</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10152,23 +10164,23 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>장태양</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>003-131-0138</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
+          <t>180-0109-8996</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>010-4693-1113</t>
+          <t>984826241072</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10178,23 +10190,31 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>전다성</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>010-873-8740</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
+          <t>009447232</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>장현준</t>
+          <t>전민찬</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>010-4102-4804</t>
+          <t>182-010-9727</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10204,40 +10224,36 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>전진우HP</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>180-0109-8996</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>전찬우HP</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>984826241072</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>010-5303-0325</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>전다성</t>
-        </is>
-      </c>
+      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>009447232</t>
+          <t>070860375123028</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10249,12 +10265,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>전민찬</t>
+          <t>제과제빵</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>182-010-9727</t>
+          <t>010-2055-6086</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10266,34 +10282,38 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>전진우</t>
+          <t>지승환HP</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>010-5303-0325</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>010-765-1744</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>전찬우</t>
-        </is>
-      </c>
+      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>010-5303-0325</t>
+          <t>010-8937-1314</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>찬HP</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>070860375123028</t>
+          <t>006-696-3680</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10303,31 +10323,23 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>제과제빵</t>
-        </is>
-      </c>
+      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>010-2055-6086</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>810-2263-3680</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>지승환</t>
+          <t>천병국HP</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>010-8937-1314</t>
+          <t>004-730-7511</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -10335,21 +10347,25 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>찬</t>
+          <t>최선을</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>810-2263-3680</t>
+          <t>010-8875-1310</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>최이서</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>010-0108-0556</t>
+          <t>003-167-4020</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -10357,25 +10373,21 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>천병국</t>
+          <t>한승진</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>010-765-1744</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
+          <t>012-3671-9316</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>004-730-7511</t>
+          <t>100102193</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -10383,12 +10395,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>최선을</t>
+          <t>한시윤</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>010-8875-1310</t>
+          <t>010-8227-9961</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -10396,141 +10408,80 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>최이서</t>
+          <t>한지홍</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>003-167-4020</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>010553209513</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>한기현</t>
-        </is>
-      </c>
+      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>010-8602-5779</t>
+          <t>010-9490-0951</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>한승진</t>
-        </is>
-      </c>
+      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>012-3671-9316</t>
+          <t>010-7132-9316</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>황도현</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>100102193</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
+          <t>764-6560-8649</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>한시윤</t>
-        </is>
-      </c>
+      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>010-8227-9961</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>010-546-2641</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>부모</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>한지홍</t>
+          <t>황현서</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>010-9490-0951</t>
+          <t>010-2384-4100</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr"/>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>010-7132-9316</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>010553209513</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>황도현</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>764-6560-8649</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr"/>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>010-546-2641</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>부모</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>황현서</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>010-2384-4100</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/수강생_정밀분석_최종본.xlsx
+++ b/수강생_정밀분석_최종본.xlsx
@@ -4299,27 +4299,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>김지우</t>
+          <t>김수연</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>남</t>
+          <t>여</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1994년 12월 18일</t>
+          <t>1991년 7월 13일</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>김포시 감정로 87, 신트리전원</t>
+          <t>인천 서구 청라 3동 505 청라에비뉴123차 4703-505</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>010-8618-3417</t>
+          <t>010-4024-4323</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -4328,36 +4328,40 @@
           <t>일반</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>한식</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026년 6월 29일 00:00</t>
+          <t>2020년 5월 26일 10:00</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>250</v>
+        <v>270000</v>
       </c>
       <c r="K63" t="n">
-        <v>20</v>
+        <v>300000</v>
       </c>
       <c r="L63" t="n">
-        <v>270</v>
+        <v>310000</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>실기책, 제과</t>
+          <t>한식 오전반 1시</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>KakaoTalk_Photo_2026-06-25-08-50-33.jpeg</t>
+          <t>CCF_000008.pdf (Page 1)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>김수연</t>
+          <t>김민정</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4367,59 +4371,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1991년 7월 13일</t>
+          <t>2009년 10월 17일</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>인천 서구 청라 3동 505 청라에비뉴123차 4703-505</t>
+          <t>김포시 풍무동 11번지 304호</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>010-4024-4323</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>010-9332-0213</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>010-4059-8273</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>풍무중학교 2학년</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>한식</t>
+          <t>제과</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2020년 5월 26일 10:00</t>
+          <t>2023년 1월 5일 10:00</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>270000</v>
+        <v>340000</v>
       </c>
       <c r="K64" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="L64" t="n">
-        <v>310000</v>
+        <v>370000</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>한식 오전반 1시</t>
+          <t>제과제빵 오전 10시</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>CCF_000008.pdf (Page 1)</t>
+          <t>CCF_000008.pdf (Page 2)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>김민정</t>
+          <t>김유미</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4429,83 +4437,79 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2009년 10월 17일</t>
+          <t>1980년 8월 7일</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>김포시 풍무동 11번지 304호</t>
+          <t>경기도 김포시 풍무로 15번길 11-011</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>010-9332-0213</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>010-4059-8273</t>
-        </is>
-      </c>
+          <t>010-3181-3818</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>풍무중학교 2학년</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>제과</t>
+          <t>한식조리사</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2023년 1월 5일 10:00</t>
+          <t>2020년 5월 1일 00:00</t>
         </is>
       </c>
       <c r="J65" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L65" t="n">
         <v>340000</v>
       </c>
-      <c r="K65" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L65" t="n">
-        <v>370000</v>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>제과제빵 오전 10시</t>
+          <t>한식조리사 (월, 수, 금) 19:00</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>CCF_000008.pdf (Page 2)</t>
+          <t>CCF_000008.pdf (Page 3)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>김유미</t>
+          <t>김지우</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>여</t>
+          <t>남</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1980년 8월 7일</t>
+          <t>1994년 12월 18일</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 15번길 11-011</t>
+          <t>김포시 감정로 87, 신트리전원</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>010-3181-3818</t>
+          <t>010-8618-3417</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -4514,33 +4518,29 @@
           <t>일반</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>한식조리사</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2020년 5월 1일 00:00</t>
+          <t>2026년 6월 29일 00:00</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>300000</v>
+        <v>250</v>
       </c>
       <c r="K66" t="n">
-        <v>40000</v>
+        <v>20</v>
       </c>
       <c r="L66" t="n">
-        <v>340000</v>
+        <v>270</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>한식조리사 (월, 수, 금) 19:00</t>
+          <t>실기책, 제과</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>CCF_000008.pdf (Page 3)</t>
+          <t>KakaoTalk_Photo_2026-06-25-08-50-33.jpeg</t>
         </is>
       </c>
     </row>

--- a/수강생_정밀분석_최종본.xlsx
+++ b/수강생_정밀분석_최종본.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>김아연</t>
+          <t>김은정</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>김기현</t>
+          <t>한</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>정다혜</t>
+          <t>연</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>김민재</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>이유진</t>
+          <t>이동규</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>이정우</t>
+          <t>이</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>신아리</t>
+          <t>연</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3211,7 +3211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>공윤</t>
+          <t>민통원</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>김시후</t>
+          <t>김시우</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5139,7 +5139,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>김태리</t>
+          <t>김태희</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>박미래</t>
+          <t>박재현</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>오예랑</t>
+          <t>손예원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5901,7 +5901,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>이지희</t>
+          <t>구</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>이재희</t>
+          <t>연</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7243,7 +7243,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>조서림</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>하지호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7417,7 +7417,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>김나윤</t>
+          <t>김기윤</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7477,7 +7477,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>송지호</t>
+          <t>송지후</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7537,7 +7537,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>박유진</t>
+          <t>연</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
